--- a/TestCases.xlsx
+++ b/TestCases.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IrctcWebAutomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8CA42A-AED9-4955-B635-CA32EBDB65BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9A2780-7ADF-4910-BE30-537A61BDC785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Automation Implementation notes" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>Test Case Id</t>
   </si>
@@ -162,12 +164,34 @@
       <t>" Password credentials</t>
     </r>
   </si>
+  <si>
+    <t>Selenium</t>
+  </si>
+  <si>
+    <t>Need to implement waits according to the flow of execution</t>
+  </si>
+  <si>
+    <t>Calander Implementation</t>
+  </si>
+  <si>
+    <t>Calander is written inside the table tag
+1. As it has tableheader and table body 
+2. So we need to write the xpath in dynamic pattern to select the date based on the user requirement</t>
+  </si>
+  <si>
+    <t>1. First find the parent note of the table 
+2. Next get the tbody tag and get the size of the tr tag using the list of webelements
+3. And now store them in the list and get the size of it</t>
+  </si>
+  <si>
+    <t>Logic to implement the calander logic</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +211,15 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -219,7 +252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -228,12 +261,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -526,30 +561,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
@@ -560,17 +595,17 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
       <c r="D3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
@@ -579,20 +614,20 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D6" t="s">
@@ -603,17 +638,17 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
       <c r="D7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
@@ -636,4 +671,57 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045CE7EB-5848-4D1A-A45D-C9976053AE13}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C3BBC67-5CF7-4196-A63A-3153EFB66690}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="86.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>